--- a/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_STRICT.xlsx
+++ b/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_STRICT.xlsx
@@ -11,7 +11,7 @@
     <sheet name="02_Feature_Groups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,14 +495,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI10"/>
+  <dimension ref="A1:BI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -529,7 +529,7 @@
     <col width="24" customWidth="1" min="29" max="29"/>
     <col width="28" customWidth="1" min="30" max="30"/>
     <col width="28" customWidth="1" min="31" max="31"/>
-    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="20" customWidth="1" min="32" max="32"/>
     <col width="21" customWidth="1" min="33" max="33"/>
     <col width="23" customWidth="1" min="34" max="34"/>
     <col width="24" customWidth="1" min="35" max="35"/>
@@ -941,11 +941,11 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>PAIR_001</t>
+          <t>PAIR_004</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1008,7 +1008,7 @@
         <v>240.4436333333333</v>
       </c>
       <c r="P5" s="5" t="n">
-        <v>41.58535677727425</v>
+        <v>42.80810564129094</v>
       </c>
       <c r="Q5" s="5" t="n">
         <v>148.1254196841063</v>
@@ -1017,61 +1017,61 @@
         <v>274.35</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>43.13601932523515</v>
+        <v>44.7845362014835</v>
       </c>
       <c r="T5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U5" s="5" t="n">
-        <v>55.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="V5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>0.2768195885045651</v>
+        <v>0</v>
       </c>
       <c r="X5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" s="5" t="n">
-        <v>0.297034431778371</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="5" t="n">
         <v>25.88333333333333</v>
       </c>
       <c r="AA5" s="5" t="n">
-        <v>13.56666666666667</v>
+        <v>69.48333333333333</v>
       </c>
       <c r="AB5" s="5" t="n">
         <v>0.3556868609874803</v>
       </c>
       <c r="AC5" s="5" t="n">
-        <v>0.5630585551044169</v>
+        <v>0.8398781436089819</v>
       </c>
       <c r="AD5" s="5" t="n">
         <v>0.8245155824564901</v>
       </c>
       <c r="AE5" s="5" t="n">
-        <v>2.49018525599005</v>
+        <v>0.7252485768751104</v>
       </c>
       <c r="AF5" s="5" t="n">
-        <v>1.25</v>
+        <v>8.15</v>
       </c>
       <c r="AG5" s="5" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AH5" s="5" t="n">
-        <v>0</v>
+        <v>0.5758500319474457</v>
       </c>
       <c r="AI5" s="5" t="n">
-        <v>0</v>
+        <v>1.797999630400208</v>
       </c>
       <c r="AJ5" s="5" t="n">
-        <v>0</v>
+        <v>4.239386738263403</v>
       </c>
       <c r="AK5" s="5" t="n">
-        <v>0</v>
+        <v>10.84220882653392</v>
       </c>
       <c r="AL5" s="5" t="n">
         <v>8.016666666666667</v>
@@ -1092,19 +1092,19 @@
         <v>20.12881815299597</v>
       </c>
       <c r="AR5" s="5" t="n">
-        <v>56.05</v>
+        <v>55.88333333333333</v>
       </c>
       <c r="AS5" s="5" t="n">
         <v>25.13333333333333</v>
       </c>
       <c r="AT5" s="5" t="n">
-        <v>44.91739841291827</v>
+        <v>44.7773945763174</v>
       </c>
       <c r="AU5" s="5" t="n">
         <v>16.04368253659841</v>
       </c>
       <c r="AV5" s="5" t="n">
-        <v>48.08285289518459</v>
+        <v>48.07593810758802</v>
       </c>
       <c r="AW5" s="5" t="n">
         <v>38.30056838975749</v>
@@ -1128,31 +1128,31 @@
         <v>42.9634053845555</v>
       </c>
       <c r="BD5" s="5" t="n">
-        <v>109.1269666666667</v>
+        <v>102.3936333333333</v>
       </c>
       <c r="BE5" s="5" t="n">
-        <v>154.5833333333333</v>
+        <v>144.6333333333333</v>
       </c>
       <c r="BF5" s="5" t="n">
-        <v>71.26833841096357</v>
+        <v>70.83249221561701</v>
       </c>
       <c r="BG5" s="5" t="n">
-        <v>113.8863544926646</v>
+        <v>112.0883548622644</v>
       </c>
       <c r="BH5" s="5" t="n">
-        <v>39.18463451586039</v>
+        <v>41.50599402114867</v>
       </c>
       <c r="BI5" s="5" t="n">
-        <v>44.20386805106121</v>
+        <v>46.49897182578381</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>PAIR_006</t>
+          <t>PAIR_010</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1215,7 +1215,7 @@
         <v>241.37365</v>
       </c>
       <c r="P6" s="7" t="n">
-        <v>43.15630919960726</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="Q6" s="7" t="n">
         <v>143.7061031155876</v>
@@ -1224,61 +1224,61 @@
         <v>241.6157666666667</v>
       </c>
       <c r="S6" s="7" t="n">
-        <v>42.008597388821</v>
+        <v>42.34188357413701</v>
       </c>
       <c r="T6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="U6" s="7" t="n">
-        <v>23.88333333333333</v>
+        <v>0</v>
       </c>
       <c r="V6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="W6" s="7" t="n">
-        <v>0.1004812886674145</v>
+        <v>0</v>
       </c>
       <c r="X6" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y6" s="7" t="n">
-        <v>0.2524303134701272</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="7" t="n">
-        <v>42.53553333333333</v>
+        <v>43.48553333333334</v>
       </c>
       <c r="AA6" s="7" t="n">
-        <v>13.1</v>
+        <v>36.98333333333333</v>
       </c>
       <c r="AB6" s="7" t="n">
-        <v>0.6596733987548126</v>
+        <v>1.332101358262426</v>
       </c>
       <c r="AC6" s="7" t="n">
-        <v>0.3335967503409809</v>
+        <v>0.4340780390083954</v>
       </c>
       <c r="AD6" s="7" t="n">
-        <v>0.9305256293629504</v>
+        <v>1.837992439533428</v>
       </c>
       <c r="AE6" s="7" t="n">
-        <v>1.527924047363271</v>
+        <v>0.7042275531456619</v>
       </c>
       <c r="AF6" s="7" t="n">
-        <v>0</v>
+        <v>7.55</v>
       </c>
       <c r="AG6" s="7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH6" s="7" t="n">
-        <v>0</v>
+        <v>0.7541054091629448</v>
       </c>
       <c r="AI6" s="7" t="n">
-        <v>0</v>
+        <v>2.038955216433607</v>
       </c>
       <c r="AJ6" s="7" t="n">
-        <v>0</v>
+        <v>5.992890668844595</v>
       </c>
       <c r="AK6" s="7" t="n">
-        <v>0</v>
+        <v>27.1860695524481</v>
       </c>
       <c r="AL6" s="7" t="n">
         <v>4.1</v>
@@ -1302,64 +1302,64 @@
         <v>52.5</v>
       </c>
       <c r="AS6" s="7" t="n">
-        <v>43.73333333333333</v>
+        <v>42.43333333333333</v>
       </c>
       <c r="AT6" s="7" t="n">
         <v>42.76805623685773</v>
       </c>
       <c r="AU6" s="7" t="n">
-        <v>31.25618145550666</v>
+        <v>30.59797914468512</v>
       </c>
       <c r="AV6" s="7" t="n">
         <v>48.87777855640883</v>
       </c>
       <c r="AW6" s="7" t="n">
-        <v>42.88195626517683</v>
+        <v>43.26501371597268</v>
       </c>
       <c r="AX6" s="7" t="n">
-        <v>38.05478333333333</v>
+        <v>37.47145</v>
       </c>
       <c r="AY6" s="7" t="n">
         <v>34.95</v>
       </c>
       <c r="AZ6" s="7" t="n">
-        <v>30.13874197108473</v>
+        <v>29.77502417243205</v>
       </c>
       <c r="BA6" s="7" t="n">
         <v>25.11354425718663</v>
       </c>
       <c r="BB6" s="7" t="n">
-        <v>47.51898079212339</v>
+        <v>47.67633625989716</v>
       </c>
       <c r="BC6" s="7" t="n">
         <v>43.11338069903283</v>
       </c>
       <c r="BD6" s="7" t="n">
-        <v>104.1833333333333</v>
+        <v>96.26666666666667</v>
       </c>
       <c r="BE6" s="7" t="n">
-        <v>124.3324333333333</v>
+        <v>121.1324333333333</v>
       </c>
       <c r="BF6" s="7" t="n">
-        <v>69.67242471935344</v>
+        <v>68.60960914933557</v>
       </c>
       <c r="BG6" s="7" t="n">
-        <v>86.63218730858281</v>
+        <v>85.25143440297076</v>
       </c>
       <c r="BH6" s="7" t="n">
-        <v>40.12489665488282</v>
+        <v>42.76222176897646</v>
       </c>
       <c r="BI6" s="7" t="n">
-        <v>41.80672009031945</v>
+        <v>42.22722126040766</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PAIR_011</t>
+          <t>PAIR_016</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1422,7 +1422,7 @@
         <v>205.6434166666667</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>48.28995397818726</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>141.6663057069586</v>
@@ -1434,55 +1434,55 @@
         <v>44.82009341634151</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>22.91666666666667</v>
+        <v>0</v>
       </c>
       <c r="U7" s="5" t="n">
-        <v>28.26666666666667</v>
+        <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>0.1193938664164262</v>
+        <v>0</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>0.1148080802474786</v>
+        <v>0</v>
       </c>
       <c r="X7" s="5" t="n">
-        <v>0.3125948502539158</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="5" t="n">
-        <v>0.2436963967517234</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="5" t="n">
-        <v>7.266666666666667</v>
+        <v>30.18333333333333</v>
       </c>
       <c r="AA7" s="5" t="n">
-        <v>3.533333333333333</v>
+        <v>31.8</v>
       </c>
       <c r="AB7" s="5" t="n">
-        <v>0.2636719486807116</v>
+        <v>0.3830658150971378</v>
       </c>
       <c r="AC7" s="5" t="n">
-        <v>0.1067528203067238</v>
+        <v>0.2215609005542024</v>
       </c>
       <c r="AD7" s="5" t="n">
-        <v>2.177107833143491</v>
+        <v>0.7614781525950834</v>
       </c>
       <c r="AE7" s="5" t="n">
-        <v>1.812783741057574</v>
+        <v>0.4180394350079291</v>
       </c>
       <c r="AF7" s="5" t="n">
-        <v>0</v>
+        <v>12.0548</v>
       </c>
       <c r="AG7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
-        <v>0</v>
+        <v>2.078327234216284</v>
       </c>
       <c r="AI7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" s="5" t="n">
-        <v>0</v>
+        <v>10.34439675921434</v>
       </c>
       <c r="AK7" s="5" t="n">
         <v>0</v>
@@ -1524,37 +1524,37 @@
         <v>42.38125376977695</v>
       </c>
       <c r="AX7" s="5" t="n">
-        <v>30.75</v>
+        <v>30.25</v>
       </c>
       <c r="AY7" s="5" t="n">
         <v>23</v>
       </c>
       <c r="AZ7" s="5" t="n">
-        <v>25.36797775428393</v>
+        <v>24.89543913557874</v>
       </c>
       <c r="BA7" s="5" t="n">
         <v>17.06985215621225</v>
       </c>
       <c r="BB7" s="5" t="n">
-        <v>49.49849317909059</v>
+        <v>49.37938340941238</v>
       </c>
       <c r="BC7" s="5" t="n">
         <v>44.53004910316239</v>
       </c>
       <c r="BD7" s="5" t="n">
-        <v>98.77674999999999</v>
+        <v>87.22195000000001</v>
       </c>
       <c r="BE7" s="5" t="n">
         <v>134.3833333333333</v>
       </c>
       <c r="BF7" s="5" t="n">
-        <v>78.83492659413233</v>
+        <v>77.22913797862124</v>
       </c>
       <c r="BG7" s="5" t="n">
         <v>102.738159054381</v>
       </c>
       <c r="BH7" s="5" t="n">
-        <v>47.88673038592523</v>
+        <v>53.12594225097322</v>
       </c>
       <c r="BI7" s="5" t="n">
         <v>45.87093793820807</v>
@@ -1562,11 +1562,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>PAIR_014</t>
+          <t>PAIR_020</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -1629,7 +1629,7 @@
         <v>184.8726166666667</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>46.49901997986691</v>
+        <v>48.60919773277766</v>
       </c>
       <c r="Q8" s="7" t="n">
         <v>126.7676219192398</v>
@@ -1638,142 +1638,142 @@
         <v>189.8237333333333</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>45.74782714011837</v>
+        <v>46.13403705248899</v>
       </c>
       <c r="T8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="U8" s="7" t="n">
-        <v>23.71666666666667</v>
+        <v>0</v>
       </c>
       <c r="V8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="W8" s="7" t="n">
-        <v>0.1169990422600451</v>
+        <v>0</v>
       </c>
       <c r="X8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="7" t="n">
-        <v>0.2959919551202828</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="7" t="n">
         <v>21.48333333333333</v>
       </c>
       <c r="AA8" s="7" t="n">
-        <v>0</v>
+        <v>23.71666666666667</v>
       </c>
       <c r="AB8" s="7" t="n">
         <v>0.237667416199215</v>
       </c>
       <c r="AC8" s="7" t="n">
-        <v>0</v>
+        <v>0.1169990422600451</v>
       </c>
       <c r="AD8" s="7" t="n">
         <v>0.6637724579652243</v>
       </c>
       <c r="AE8" s="7" t="n">
-        <v>0</v>
+        <v>0.2959919551202828</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>0.08333333333333333</v>
+        <v>8.303566666666667</v>
       </c>
       <c r="AG8" s="7" t="n">
-        <v>0</v>
+        <v>2.383333333333333</v>
       </c>
       <c r="AH8" s="7" t="n">
-        <v>0</v>
+        <v>0.9162394150268994</v>
       </c>
       <c r="AI8" s="7" t="n">
-        <v>0</v>
+        <v>0.7633432107826125</v>
       </c>
       <c r="AJ8" s="7" t="n">
-        <v>0</v>
+        <v>6.620572473067472</v>
       </c>
       <c r="AK8" s="7" t="n">
-        <v>0</v>
+        <v>19.21703187984199</v>
       </c>
       <c r="AL8" s="7" t="n">
         <v>1.683333333333333</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>2.633333333333333</v>
+        <v>1.633333333333333</v>
       </c>
       <c r="AN8" s="7" t="n">
         <v>0.3011879778687425</v>
       </c>
       <c r="AO8" s="7" t="n">
-        <v>0.2267712765180789</v>
+        <v>0.122404176435325</v>
       </c>
       <c r="AP8" s="7" t="n">
         <v>10.73541307254924</v>
       </c>
       <c r="AQ8" s="7" t="n">
-        <v>5.166940477627115</v>
+        <v>4.496479950685409</v>
       </c>
       <c r="AR8" s="7" t="n">
         <v>48.91905</v>
       </c>
       <c r="AS8" s="7" t="n">
-        <v>45.67373333333333</v>
+        <v>45.25706666666667</v>
       </c>
       <c r="AT8" s="7" t="n">
         <v>38.90083595250158</v>
       </c>
       <c r="AU8" s="7" t="n">
-        <v>34.23732716182031</v>
+        <v>33.99612977910262</v>
       </c>
       <c r="AV8" s="7" t="n">
         <v>47.71249967344205</v>
       </c>
       <c r="AW8" s="7" t="n">
-        <v>44.97638970559049</v>
+        <v>45.07070247768651</v>
       </c>
       <c r="AX8" s="7" t="n">
-        <v>35.46666666666667</v>
+        <v>35.13333333333333</v>
       </c>
       <c r="AY8" s="7" t="n">
         <v>29.9</v>
       </c>
       <c r="AZ8" s="7" t="n">
-        <v>27.95827681357427</v>
+        <v>27.71428406489335</v>
       </c>
       <c r="BA8" s="7" t="n">
         <v>22.79241179514765</v>
       </c>
       <c r="BB8" s="7" t="n">
-        <v>47.29783671469331</v>
+        <v>47.32989688501711</v>
       </c>
       <c r="BC8" s="7" t="n">
         <v>45.73728119427622</v>
       </c>
       <c r="BD8" s="7" t="n">
-        <v>77.23690000000001</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="BE8" s="7" t="n">
-        <v>87.90000000000001</v>
+        <v>86.93333333333334</v>
       </c>
       <c r="BF8" s="7" t="n">
-        <v>59.39914312074116</v>
+        <v>58.72689645439518</v>
       </c>
       <c r="BG8" s="7" t="n">
-        <v>69.39411264349368</v>
+        <v>68.97633391551152</v>
       </c>
       <c r="BH8" s="7" t="n">
-        <v>46.14308170375131</v>
+        <v>50.80913896559064</v>
       </c>
       <c r="BI8" s="7" t="n">
-        <v>47.36799497849398</v>
+        <v>47.60636543248494</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PAIR_017</t>
+          <t>PAIR_024</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1836,7 +1836,7 @@
         <v>195.4022</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>46.86485275946674</v>
+        <v>48.03268705989514</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>145.9943306994593</v>
@@ -1845,61 +1845,61 @@
         <v>266.8632166666667</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>44.5741238531821</v>
+        <v>45.34276468747346</v>
       </c>
       <c r="T9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="U9" s="5" t="n">
-        <v>59.81666666666667</v>
+        <v>0</v>
       </c>
       <c r="V9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>0.2256049681381114</v>
+        <v>0</v>
       </c>
       <c r="X9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Y9" s="5" t="n">
-        <v>0.2262964294503207</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="5" t="n">
         <v>8.933333333333334</v>
       </c>
       <c r="AA9" s="5" t="n">
-        <v>11.26666666666667</v>
+        <v>71.08333333333333</v>
       </c>
       <c r="AB9" s="5" t="n">
         <v>0.2591759316479205</v>
       </c>
       <c r="AC9" s="5" t="n">
-        <v>0.323446270295476</v>
+        <v>0.5490512384335874</v>
       </c>
       <c r="AD9" s="5" t="n">
         <v>1.740733869277078</v>
       </c>
       <c r="AE9" s="5" t="n">
-        <v>1.722494930567623</v>
+        <v>0.4634430148560175</v>
       </c>
       <c r="AF9" s="5" t="n">
-        <v>0</v>
+        <v>5.418866666666667</v>
       </c>
       <c r="AG9" s="5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH9" s="5" t="n">
-        <v>0</v>
+        <v>0.7086331393992357</v>
       </c>
       <c r="AI9" s="5" t="n">
-        <v>0</v>
+        <v>0.5525630686911562</v>
       </c>
       <c r="AJ9" s="5" t="n">
-        <v>0</v>
+        <v>7.846287974844827</v>
       </c>
       <c r="AK9" s="5" t="n">
-        <v>0</v>
+        <v>8.186119536165277</v>
       </c>
       <c r="AL9" s="5" t="n">
         <v>0</v>
@@ -1920,19 +1920,19 @@
         <v>5.347290192948117</v>
       </c>
       <c r="AR9" s="5" t="n">
-        <v>47.05</v>
+        <v>46.88333333333333</v>
       </c>
       <c r="AS9" s="5" t="n">
         <v>38.68333333333333</v>
       </c>
       <c r="AT9" s="5" t="n">
-        <v>37.71427916549126</v>
+        <v>37.60330466808259</v>
       </c>
       <c r="AU9" s="5" t="n">
         <v>27.60990969505806</v>
       </c>
       <c r="AV9" s="5" t="n">
-        <v>48.09472369669449</v>
+        <v>48.12367465520702</v>
       </c>
       <c r="AW9" s="5" t="n">
         <v>42.82450448177899</v>
@@ -1941,46 +1941,46 @@
         <v>35.66666666666666</v>
       </c>
       <c r="AY9" s="5" t="n">
-        <v>27.13333333333333</v>
+        <v>26.81666666666667</v>
       </c>
       <c r="AZ9" s="5" t="n">
         <v>27.74280476419689</v>
       </c>
       <c r="BA9" s="5" t="n">
-        <v>19.99447365781878</v>
+        <v>19.89292827190748</v>
       </c>
       <c r="BB9" s="5" t="n">
         <v>46.67013885565834</v>
       </c>
       <c r="BC9" s="5" t="n">
-        <v>44.21382381335849</v>
+        <v>44.50872702229143</v>
       </c>
       <c r="BD9" s="5" t="n">
-        <v>103.7522</v>
+        <v>98.5</v>
       </c>
       <c r="BE9" s="5" t="n">
-        <v>120.7166666666667</v>
+        <v>116.9833333333333</v>
       </c>
       <c r="BF9" s="5" t="n">
-        <v>80.19018241294468</v>
+        <v>79.5925237709541</v>
       </c>
       <c r="BG9" s="5" t="n">
-        <v>97.0168296725888</v>
+        <v>96.56581198980894</v>
       </c>
       <c r="BH9" s="5" t="n">
-        <v>46.3740618972579</v>
+        <v>48.48275559652027</v>
       </c>
       <c r="BI9" s="5" t="n">
-        <v>48.22043170251548</v>
+        <v>49.52798449398949</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>PAIR_018</t>
+          <t>PAIR_026</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2043,7 +2043,7 @@
         <v>187.65295</v>
       </c>
       <c r="P10" s="7" t="n">
-        <v>46.87226586428536</v>
+        <v>46.88285886366883</v>
       </c>
       <c r="Q10" s="7" t="n">
         <v>123.9802750677086</v>
@@ -2052,61 +2052,61 @@
         <v>194.9584</v>
       </c>
       <c r="S10" s="7" t="n">
-        <v>42.81877758960633</v>
+        <v>42.76169445348732</v>
       </c>
       <c r="T10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="U10" s="7" t="n">
-        <v>21.38333333333333</v>
+        <v>0</v>
       </c>
       <c r="V10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="W10" s="7" t="n">
-        <v>0.1090721560237224</v>
+        <v>0</v>
       </c>
       <c r="X10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Y10" s="7" t="n">
-        <v>0.3060481384921284</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="7" t="n">
         <v>29.48333333333333</v>
       </c>
       <c r="AA10" s="7" t="n">
-        <v>0</v>
+        <v>21.38333333333333</v>
       </c>
       <c r="AB10" s="7" t="n">
         <v>0.4298392460953699</v>
       </c>
       <c r="AC10" s="7" t="n">
-        <v>0</v>
+        <v>0.1090721560237224</v>
       </c>
       <c r="AD10" s="7" t="n">
         <v>0.8747435194705098</v>
       </c>
       <c r="AE10" s="7" t="n">
-        <v>0</v>
+        <v>0.3060481384921284</v>
       </c>
       <c r="AF10" s="7" t="n">
-        <v>0</v>
+        <v>0.1105833333333333</v>
       </c>
       <c r="AG10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" s="7" t="n">
-        <v>0</v>
+        <v>0.05848286929177889</v>
       </c>
       <c r="AI10" s="7" t="n">
-        <v>0</v>
+        <v>0.8778317268481433</v>
       </c>
       <c r="AJ10" s="7" t="n">
-        <v>0</v>
+        <v>31.73147391867431</v>
       </c>
       <c r="AK10" s="7" t="n">
-        <v>0</v>
+        <v>52.6699036108886</v>
       </c>
       <c r="AL10" s="7" t="n">
         <v>5.266666666666667</v>
@@ -2127,62 +2127,890 @@
         <v>0</v>
       </c>
       <c r="AR10" s="7" t="n">
-        <v>45.59391666666667</v>
+        <v>45.48333333333333</v>
       </c>
       <c r="AS10" s="7" t="n">
-        <v>39.51666666666667</v>
+        <v>39.18333333333333</v>
       </c>
       <c r="AT10" s="7" t="n">
-        <v>37.16754455699814</v>
+        <v>37.10906168770636</v>
       </c>
       <c r="AU10" s="7" t="n">
-        <v>28.52077529734963</v>
+        <v>28.21320161975721</v>
       </c>
       <c r="AV10" s="7" t="n">
-        <v>48.9111889580274</v>
+        <v>48.95295788777681</v>
       </c>
       <c r="AW10" s="7" t="n">
-        <v>43.30442474502684</v>
+        <v>43.20183999622542</v>
       </c>
       <c r="AX10" s="7" t="n">
         <v>28.73333333333333</v>
       </c>
       <c r="AY10" s="7" t="n">
-        <v>30.8</v>
+        <v>30.46666666666667</v>
       </c>
       <c r="AZ10" s="7" t="n">
         <v>23.38414305111067</v>
       </c>
       <c r="BA10" s="7" t="n">
-        <v>21.13389550628888</v>
+        <v>20.93633895165053</v>
       </c>
       <c r="BB10" s="7" t="n">
         <v>48.82999709048632</v>
       </c>
       <c r="BC10" s="7" t="n">
-        <v>41.16992631095236</v>
+        <v>41.23130209296603</v>
       </c>
       <c r="BD10" s="7" t="n">
         <v>78.57570000000001</v>
       </c>
       <c r="BE10" s="7" t="n">
-        <v>103.2584</v>
+        <v>102.9250666666667</v>
       </c>
       <c r="BF10" s="7" t="n">
         <v>62.65629452354004</v>
       </c>
       <c r="BG10" s="7" t="n">
-        <v>74.21653210804637</v>
+        <v>73.84383061342899</v>
       </c>
       <c r="BH10" s="7" t="n">
         <v>47.84402393376581</v>
       </c>
       <c r="BI10" s="7" t="n">
-        <v>43.12474265031012</v>
+        <v>43.04714080151908</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_032</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Maduravoyal ↔ Silk Board</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Silk Board → Maduravoyal</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>00:27:57</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>04:39:51</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>23:26:13</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>03:20:51</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>61.73333333333335</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>240.4425765887812</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>251.8893</v>
+      </c>
+      <c r="P11" s="5" t="n">
+        <v>64.24069875201077</v>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>240.7230050078111</v>
+      </c>
+      <c r="R11" s="5" t="n">
+        <v>234.6249833333333</v>
+      </c>
+      <c r="S11" s="5" t="n">
+        <v>68.13871680530009</v>
+      </c>
+      <c r="T11" s="5" t="n">
+        <v>21.51666666666667</v>
+      </c>
+      <c r="U11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="5" t="n">
+        <v>0.814768997799896</v>
+      </c>
+      <c r="W11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="5" t="n">
+        <v>2.272012697195682</v>
+      </c>
+      <c r="Y11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="5" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AA11" s="5" t="n">
+        <v>16.43333333333333</v>
+      </c>
+      <c r="AB11" s="5" t="n">
+        <v>0.1409484311311202</v>
+      </c>
+      <c r="AC11" s="5" t="n">
+        <v>0.08388219724002884</v>
+      </c>
+      <c r="AD11" s="5" t="n">
+        <v>2.306428873054694</v>
+      </c>
+      <c r="AE11" s="5" t="n">
+        <v>0.3062636004706936</v>
+      </c>
+      <c r="AF11" s="5" t="n">
+        <v>3.033333333333333</v>
+      </c>
+      <c r="AG11" s="5" t="n">
+        <v>6.316666666666666</v>
+      </c>
+      <c r="AH11" s="5" t="n">
+        <v>0.005421542589709919</v>
+      </c>
+      <c r="AI11" s="5" t="n">
+        <v>0.02429801927644335</v>
+      </c>
+      <c r="AJ11" s="5" t="n">
+        <v>0.1072393039722841</v>
+      </c>
+      <c r="AK11" s="5" t="n">
+        <v>0.2307991276918102</v>
+      </c>
+      <c r="AL11" s="5" t="n">
+        <v>7.283333333333333</v>
+      </c>
+      <c r="AM11" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN11" s="5" t="n">
+        <v>0.9244772773315977</v>
+      </c>
+      <c r="AO11" s="5" t="n">
+        <v>0.2309310830082773</v>
+      </c>
+      <c r="AP11" s="5" t="n">
+        <v>7.61583111760584</v>
+      </c>
+      <c r="AQ11" s="5" t="n">
+        <v>2.771172996099328</v>
+      </c>
+      <c r="AR11" s="5" t="n">
+        <v>30.68333333333333</v>
+      </c>
+      <c r="AS11" s="5" t="n">
+        <v>43.75068333333333</v>
+      </c>
+      <c r="AT11" s="5" t="n">
+        <v>28.50220385729329</v>
+      </c>
+      <c r="AU11" s="5" t="n">
+        <v>43.296144650172</v>
+      </c>
+      <c r="AV11" s="5" t="n">
+        <v>55.73489075842252</v>
+      </c>
+      <c r="AW11" s="5" t="n">
+        <v>59.37664239934509</v>
+      </c>
+      <c r="AX11" s="5" t="n">
+        <v>27.88333333333333</v>
+      </c>
+      <c r="AY11" s="5" t="n">
+        <v>31.78333333333333</v>
+      </c>
+      <c r="AZ11" s="5" t="n">
+        <v>26.94936248085756</v>
+      </c>
+      <c r="BA11" s="5" t="n">
+        <v>33.18950889523448</v>
+      </c>
+      <c r="BB11" s="5" t="n">
+        <v>57.99025997076343</v>
+      </c>
+      <c r="BC11" s="5" t="n">
+        <v>62.65455271255593</v>
+      </c>
+      <c r="BD11" s="5" t="n">
+        <v>157.8226333333333</v>
+      </c>
+      <c r="BE11" s="5" t="n">
+        <v>131.3409666666667</v>
+      </c>
+      <c r="BF11" s="5" t="n">
+        <v>183.105394001778</v>
+      </c>
+      <c r="BG11" s="5" t="n">
+        <v>163.8982401628798</v>
+      </c>
+      <c r="BH11" s="5" t="n">
+        <v>69.61183835339216</v>
+      </c>
+      <c r="BI11" s="5" t="n">
+        <v>74.87301684576799</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_033</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>23:17:00</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>02:21:52</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>23:27:11</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>02:36:16</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>10.18333333333339</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>159.8172074707595</v>
+      </c>
+      <c r="O12" s="7" t="n">
+        <v>184.8808833333333</v>
+      </c>
+      <c r="P12" s="7" t="n">
+        <v>58.20216621959079</v>
+      </c>
+      <c r="Q12" s="7" t="n">
+        <v>159.58380997156</v>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v>189.0966166666667</v>
+      </c>
+      <c r="S12" s="7" t="n">
+        <v>55.92805804691302</v>
+      </c>
+      <c r="T12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AA12" s="7" t="n">
+        <v>14.68333333333333</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>0.06497427594259966</v>
+      </c>
+      <c r="AC12" s="7" t="n">
+        <v>0.1830132758657204</v>
+      </c>
+      <c r="AD12" s="7" t="n">
+        <v>0.9869510269761974</v>
+      </c>
+      <c r="AE12" s="7" t="n">
+        <v>0.7478408548428984</v>
+      </c>
+      <c r="AF12" s="7" t="n">
+        <v>16.35</v>
+      </c>
+      <c r="AG12" s="7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AH12" s="7" t="n">
+        <v>0.1028343892545171</v>
+      </c>
+      <c r="AI12" s="7" t="n">
+        <v>0.04005612640255141</v>
+      </c>
+      <c r="AJ12" s="7" t="n">
+        <v>0.3773739055211637</v>
+      </c>
+      <c r="AK12" s="7" t="n">
+        <v>0.6966282852617637</v>
+      </c>
+      <c r="AL12" s="7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AM12" s="7" t="n">
+        <v>10.68333333333333</v>
+      </c>
+      <c r="AN12" s="7" t="n">
+        <v>0.2821742444234817</v>
+      </c>
+      <c r="AO12" s="7" t="n">
+        <v>0.6170753744976548</v>
+      </c>
+      <c r="AP12" s="7" t="n">
+        <v>5.209370666279662</v>
+      </c>
+      <c r="AQ12" s="7" t="n">
+        <v>3.465633928535972</v>
+      </c>
+      <c r="AR12" s="7" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="AS12" s="7" t="n">
+        <v>26.06666666666667</v>
+      </c>
+      <c r="AT12" s="7" t="n">
+        <v>34.54349490383015</v>
+      </c>
+      <c r="AU12" s="7" t="n">
+        <v>22.28483087263108</v>
+      </c>
+      <c r="AV12" s="7" t="n">
+        <v>51.55745508034351</v>
+      </c>
+      <c r="AW12" s="7" t="n">
+        <v>51.29500712370324</v>
+      </c>
+      <c r="AX12" s="7" t="n">
+        <v>29.63088333333333</v>
+      </c>
+      <c r="AY12" s="7" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AZ12" s="7" t="n">
+        <v>26.48638220201241</v>
+      </c>
+      <c r="BA12" s="7" t="n">
+        <v>19.99284056290314</v>
+      </c>
+      <c r="BB12" s="7" t="n">
+        <v>53.63265462737621</v>
+      </c>
+      <c r="BC12" s="7" t="n">
+        <v>53.1175099826209</v>
+      </c>
+      <c r="BD12" s="7" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="BE12" s="7" t="n">
+        <v>111.62995</v>
+      </c>
+      <c r="BF12" s="7" t="n">
+        <v>98.33734745529641</v>
+      </c>
+      <c r="BG12" s="7" t="n">
+        <v>116.4659937592599</v>
+      </c>
+      <c r="BH12" s="7" t="n">
+        <v>64.48350652806322</v>
+      </c>
+      <c r="BI12" s="7" t="n">
+        <v>62.59932594752209</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>13-09-2026</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>04:07:02</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>04:20:12</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>02:26:26</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>02:40:28</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>17.5104260598227</v>
+      </c>
+      <c r="O13" s="5" t="n">
+        <v>13.15565</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>79.86116714790693</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>17.59592292311513</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>14.03436666666667</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>75.22643525442838</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="5" t="n">
+        <v>2.366666666666667</v>
+      </c>
+      <c r="AS13" s="5" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AT13" s="5" t="n">
+        <v>3.068290636520454</v>
+      </c>
+      <c r="AU13" s="5" t="n">
+        <v>0.6703253541496691</v>
+      </c>
+      <c r="AV13" s="5" t="n">
+        <v>77.78764993995516</v>
+      </c>
+      <c r="AW13" s="5" t="n">
+        <v>68.9477507125374</v>
+      </c>
+      <c r="AX13" s="5" t="n">
+        <v>1.683333333333333</v>
+      </c>
+      <c r="AY13" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AZ13" s="5" t="n">
+        <v>2.206663901320678</v>
+      </c>
+      <c r="BA13" s="5" t="n">
+        <v>0.4473149966220811</v>
+      </c>
+      <c r="BB13" s="5" t="n">
+        <v>78.65336677974695</v>
+      </c>
+      <c r="BC13" s="5" t="n">
+        <v>76.68257084949961</v>
+      </c>
+      <c r="BD13" s="5" t="n">
+        <v>9.105650000000001</v>
+      </c>
+      <c r="BE13" s="5" t="n">
+        <v>13.10103333333333</v>
+      </c>
+      <c r="BF13" s="5" t="n">
+        <v>12.23547152198156</v>
+      </c>
+      <c r="BG13" s="5" t="n">
+        <v>16.47828257234338</v>
+      </c>
+      <c r="BH13" s="5" t="n">
+        <v>80.62338123240994</v>
+      </c>
+      <c r="BI13" s="5" t="n">
+        <v>75.46709707432262</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_038</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>13:53:57</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>16:28:14</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>14:44:32</t>
+        </is>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>16:14:25</t>
+        </is>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>50.58333333333326</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>118.6528555237152</v>
+      </c>
+      <c r="O14" s="7" t="n">
+        <v>154.2935833333334</v>
+      </c>
+      <c r="P14" s="7" t="n">
+        <v>76.62526023529979</v>
+      </c>
+      <c r="Q14" s="7" t="n">
+        <v>118.3205529638225</v>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v>89.89455</v>
+      </c>
+      <c r="S14" s="7" t="n">
+        <v>78.97289855535573</v>
+      </c>
+      <c r="T14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="7" t="n">
+        <v>57.05</v>
+      </c>
+      <c r="AA14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="7" t="n">
+        <v>0.09002709918491375</v>
+      </c>
+      <c r="AC14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="7" t="n">
+        <v>0.0946823129026262</v>
+      </c>
+      <c r="AE14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="7" t="n">
+        <v>0.1211416233489353</v>
+      </c>
+      <c r="AI14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="7" t="n">
+        <v>1.615221644652471</v>
+      </c>
+      <c r="AK14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="7" t="n">
+        <v>0.3166666666666667</v>
+      </c>
+      <c r="AM14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" s="7" t="n">
+        <v>0.01887125568339211</v>
+      </c>
+      <c r="AO14" s="7" t="n">
+        <v>0.03644173622497521</v>
+      </c>
+      <c r="AP14" s="7" t="n">
+        <v>3.575606340011136</v>
+      </c>
+      <c r="AQ14" s="7" t="n">
+        <v>2.186504173498513</v>
+      </c>
+      <c r="AR14" s="7" t="n">
+        <v>19.22816666666667</v>
+      </c>
+      <c r="AS14" s="7" t="n">
+        <v>14.0627</v>
+      </c>
+      <c r="AT14" s="7" t="n">
+        <v>21.56383013715203</v>
+      </c>
+      <c r="AU14" s="7" t="n">
+        <v>15.34811928295864</v>
+      </c>
+      <c r="AV14" s="7" t="n">
+        <v>67.28825637194332</v>
+      </c>
+      <c r="AW14" s="7" t="n">
+        <v>65.48437760725311</v>
+      </c>
+      <c r="AX14" s="7" t="n">
+        <v>15.13208333333333</v>
+      </c>
+      <c r="AY14" s="7" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="AZ14" s="7" t="n">
+        <v>17.72416642729523</v>
+      </c>
+      <c r="BA14" s="7" t="n">
+        <v>11.19959394493595</v>
+      </c>
+      <c r="BB14" s="7" t="n">
+        <v>70.27783036953805</v>
+      </c>
+      <c r="BC14" s="7" t="n">
+        <v>66.53224125704524</v>
+      </c>
+      <c r="BD14" s="7" t="n">
+        <v>58.06666666666667</v>
+      </c>
+      <c r="BE14" s="7" t="n">
+        <v>64.73184999999999</v>
+      </c>
+      <c r="BF14" s="7" t="n">
+        <v>79.13481898105066</v>
+      </c>
+      <c r="BG14" s="7" t="n">
+        <v>91.736397999703</v>
+      </c>
+      <c r="BH14" s="7" t="n">
+        <v>81.76961777605693</v>
+      </c>
+      <c r="BI14" s="7" t="n">
+        <v>85.03053566338951</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BI10"/>
+  <autoFilter ref="A4:BI14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:BI1"/>
   </mergeCells>
@@ -2388,7 +3216,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">

--- a/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_STRICT.xlsx
+++ b/Data/Results/Master_Summary/Training_Data/EV_ICE_Training_STRICT.xlsx
@@ -11,7 +11,7 @@
     <sheet name="02_Feature_Groups" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Training_Data'!$A$4:$BI$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI14"/>
+  <dimension ref="A1:BI18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1148,11 +1148,11 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>PAIR_010</t>
+          <t>PAIR_011</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -1355,11 +1355,11 @@
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>PAIR_016</t>
+          <t>PAIR_018</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1562,11 +1562,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>PAIR_020</t>
+          <t>PAIR_023</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>17:19:31</t>
+          <t>17:57:41</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>19:30:23</t>
+          <t>20:12:27</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
@@ -1623,22 +1623,22 @@
         <v>125.9333333333334</v>
       </c>
       <c r="N8" s="7" t="n">
-        <v>126.797111280885</v>
+        <v>137.8478512787692</v>
       </c>
       <c r="O8" s="7" t="n">
-        <v>184.8726166666667</v>
+        <v>223.05115</v>
       </c>
       <c r="P8" s="7" t="n">
-        <v>48.60919773277766</v>
+        <v>43.48920820013006</v>
       </c>
       <c r="Q8" s="7" t="n">
-        <v>126.7676219192398</v>
+        <v>137.9112374368539</v>
       </c>
       <c r="R8" s="7" t="n">
-        <v>189.8237333333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="S8" s="7" t="n">
-        <v>46.13403705248899</v>
+        <v>40.29129762507425</v>
       </c>
       <c r="T8" s="7" t="n">
         <v>0</v>
@@ -1659,121 +1659,121 @@
         <v>0</v>
       </c>
       <c r="Z8" s="7" t="n">
-        <v>21.48333333333333</v>
+        <v>24.65</v>
       </c>
       <c r="AA8" s="7" t="n">
         <v>23.71666666666667</v>
       </c>
       <c r="AB8" s="7" t="n">
-        <v>0.237667416199215</v>
+        <v>0.3429025418670396</v>
       </c>
       <c r="AC8" s="7" t="n">
         <v>0.1169990422600451</v>
       </c>
       <c r="AD8" s="7" t="n">
-        <v>0.6637724579652243</v>
+        <v>0.8346512175262628</v>
       </c>
       <c r="AE8" s="7" t="n">
         <v>0.2959919551202828</v>
       </c>
       <c r="AF8" s="7" t="n">
-        <v>8.303566666666667</v>
+        <v>10.13448333333333</v>
       </c>
       <c r="AG8" s="7" t="n">
-        <v>2.383333333333333</v>
+        <v>4.433333333333334</v>
       </c>
       <c r="AH8" s="7" t="n">
-        <v>0.9162394150268994</v>
+        <v>1.045477673383005</v>
       </c>
       <c r="AI8" s="7" t="n">
-        <v>0.7633432107826125</v>
+        <v>0.9828989032306129</v>
       </c>
       <c r="AJ8" s="7" t="n">
-        <v>6.620572473067472</v>
+        <v>6.18962588814562</v>
       </c>
       <c r="AK8" s="7" t="n">
-        <v>19.21703187984199</v>
+        <v>13.30239117154213</v>
       </c>
       <c r="AL8" s="7" t="n">
-        <v>1.683333333333333</v>
+        <v>2.1</v>
       </c>
       <c r="AM8" s="7" t="n">
-        <v>1.633333333333333</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="AN8" s="7" t="n">
-        <v>0.3011879778687425</v>
+        <v>0.404320010061295</v>
       </c>
       <c r="AO8" s="7" t="n">
-        <v>0.122404176435325</v>
+        <v>0.7649615744786004</v>
       </c>
       <c r="AP8" s="7" t="n">
-        <v>10.73541307254924</v>
+        <v>11.55200028746557</v>
       </c>
       <c r="AQ8" s="7" t="n">
-        <v>4.496479950685409</v>
+        <v>4.806041305624714</v>
       </c>
       <c r="AR8" s="7" t="n">
-        <v>48.91905</v>
+        <v>53.91666666666666</v>
       </c>
       <c r="AS8" s="7" t="n">
-        <v>45.25706666666667</v>
+        <v>50.65</v>
       </c>
       <c r="AT8" s="7" t="n">
-        <v>38.90083595250158</v>
+        <v>41.47108157057156</v>
       </c>
       <c r="AU8" s="7" t="n">
-        <v>33.99612977910262</v>
+        <v>36.71220944491618</v>
       </c>
       <c r="AV8" s="7" t="n">
-        <v>47.71249967344205</v>
+        <v>46.15019896570561</v>
       </c>
       <c r="AW8" s="7" t="n">
-        <v>45.07070247768651</v>
+        <v>43.4892905566628</v>
       </c>
       <c r="AX8" s="7" t="n">
-        <v>35.13333333333333</v>
+        <v>40.75</v>
       </c>
       <c r="AY8" s="7" t="n">
-        <v>29.9</v>
+        <v>34.23333333333333</v>
       </c>
       <c r="AZ8" s="7" t="n">
-        <v>27.71428406489335</v>
+        <v>30.61488043519312</v>
       </c>
       <c r="BA8" s="7" t="n">
-        <v>22.79241179514765</v>
+        <v>25.04052735423578</v>
       </c>
       <c r="BB8" s="7" t="n">
-        <v>47.32989688501711</v>
+        <v>45.07712456715551</v>
       </c>
       <c r="BC8" s="7" t="n">
-        <v>45.73728119427622</v>
+        <v>43.8879739412117</v>
       </c>
       <c r="BD8" s="7" t="n">
-        <v>69.34999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="BE8" s="7" t="n">
-        <v>86.93333333333334</v>
+        <v>109.3</v>
       </c>
       <c r="BF8" s="7" t="n">
-        <v>58.72689645439518</v>
+        <v>63.96918904769321</v>
       </c>
       <c r="BG8" s="7" t="n">
-        <v>68.97633391551152</v>
+        <v>74.29364111773266</v>
       </c>
       <c r="BH8" s="7" t="n">
-        <v>50.80913896559064</v>
+        <v>41.94700921160211</v>
       </c>
       <c r="BI8" s="7" t="n">
-        <v>47.60636543248494</v>
+        <v>40.78333455685233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PAIR_024</t>
+          <t>PAIR_028</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1976,11 +1976,11 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>PAIR_026</t>
+          <t>PAIR_031</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -2183,11 +2183,11 @@
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PAIR_032</t>
+          <t>PAIR_037</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>00:27:57</t>
+          <t>00:18:27</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>23:26:13</t>
+          <t>23:15:55</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -2241,40 +2241,40 @@
         </is>
       </c>
       <c r="M11" s="5" t="n">
-        <v>61.73333333333335</v>
+        <v>62.5333333333333</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>240.4425765887812</v>
+        <v>249.1268483717951</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>251.8893</v>
+        <v>261.38705</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>64.24069875201077</v>
+        <v>63.84368844822295</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>240.7230050078111</v>
+        <v>249.9072012121763</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>234.6249833333333</v>
+        <v>244.9409666666667</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>68.13871680530009</v>
+        <v>67.45522324597772</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>21.51666666666667</v>
+        <v>20.98333333333333</v>
       </c>
       <c r="U11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>0.814768997799896</v>
+        <v>0.3053571304336727</v>
       </c>
       <c r="W11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X11" s="5" t="n">
-        <v>2.272012697195682</v>
+        <v>0.8731419138691198</v>
       </c>
       <c r="Y11" s="5" t="n">
         <v>0</v>
@@ -2334,67 +2334,67 @@
         <v>2.771172996099328</v>
       </c>
       <c r="AR11" s="5" t="n">
-        <v>30.68333333333333</v>
+        <v>33.00371666666667</v>
       </c>
       <c r="AS11" s="5" t="n">
-        <v>43.75068333333333</v>
+        <v>46.8</v>
       </c>
       <c r="AT11" s="5" t="n">
-        <v>28.50220385729329</v>
+        <v>30.51433266428049</v>
       </c>
       <c r="AU11" s="5" t="n">
-        <v>43.296144650172</v>
+        <v>45.48619791337757</v>
       </c>
       <c r="AV11" s="5" t="n">
-        <v>55.73489075842252</v>
+        <v>55.47435697464869</v>
       </c>
       <c r="AW11" s="5" t="n">
-        <v>59.37664239934509</v>
+        <v>58.31563835048407</v>
       </c>
       <c r="AX11" s="5" t="n">
-        <v>27.88333333333333</v>
+        <v>29.65</v>
       </c>
       <c r="AY11" s="5" t="n">
-        <v>31.78333333333333</v>
+        <v>33.41666666666666</v>
       </c>
       <c r="AZ11" s="5" t="n">
-        <v>26.94936248085756</v>
+        <v>28.67599222426386</v>
       </c>
       <c r="BA11" s="5" t="n">
-        <v>33.18950889523448</v>
+        <v>34.42847320024024</v>
       </c>
       <c r="BB11" s="5" t="n">
-        <v>57.99025997076343</v>
+        <v>58.02898932397409</v>
       </c>
       <c r="BC11" s="5" t="n">
-        <v>62.65455271255593</v>
+        <v>61.81670998546878</v>
       </c>
       <c r="BD11" s="5" t="n">
-        <v>157.8226333333333</v>
+        <v>163.7666666666667</v>
       </c>
       <c r="BE11" s="5" t="n">
-        <v>131.3409666666667</v>
+        <v>136.9743</v>
       </c>
       <c r="BF11" s="5" t="n">
-        <v>183.105394001778</v>
+        <v>188.5603191017646</v>
       </c>
       <c r="BG11" s="5" t="n">
-        <v>163.8982401628798</v>
+        <v>169.6534187990338</v>
       </c>
       <c r="BH11" s="5" t="n">
-        <v>69.61183835339216</v>
+        <v>69.08377251845639</v>
       </c>
       <c r="BI11" s="5" t="n">
-        <v>74.87301684576799</v>
+        <v>74.31470814555745</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>PAIR_033</t>
+          <t>PAIR_038</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>02:21:52</t>
+          <t>05:52:00</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>02:36:16</t>
+          <t>05:42:08</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -2451,157 +2451,157 @@
         <v>10.18333333333339</v>
       </c>
       <c r="N12" s="7" t="n">
-        <v>159.8172074707595</v>
+        <v>326.3547725745892</v>
       </c>
       <c r="O12" s="7" t="n">
-        <v>184.8808833333333</v>
+        <v>395</v>
       </c>
       <c r="P12" s="7" t="n">
-        <v>58.20216621959079</v>
+        <v>61.31623721877904</v>
       </c>
       <c r="Q12" s="7" t="n">
-        <v>159.58380997156</v>
+        <v>325.9460971942599</v>
       </c>
       <c r="R12" s="7" t="n">
-        <v>189.0966166666667</v>
+        <v>374.9615166666666</v>
       </c>
       <c r="S12" s="7" t="n">
-        <v>55.92805804691302</v>
+        <v>59.54001701508474</v>
       </c>
       <c r="T12" s="7" t="n">
-        <v>0</v>
+        <v>50.36666666666667</v>
       </c>
       <c r="U12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="V12" s="7" t="n">
-        <v>0</v>
+        <v>0.1423627546916193</v>
       </c>
       <c r="W12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="X12" s="7" t="n">
-        <v>0</v>
+        <v>0.1695916336498443</v>
       </c>
       <c r="Y12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="7" t="n">
-        <v>3.95</v>
+        <v>8.366666666666667</v>
       </c>
       <c r="AA12" s="7" t="n">
-        <v>14.68333333333333</v>
+        <v>42.65</v>
       </c>
       <c r="AB12" s="7" t="n">
-        <v>0.06497427594259966</v>
+        <v>0.1908765853606127</v>
       </c>
       <c r="AC12" s="7" t="n">
-        <v>0.1830132758657204</v>
+        <v>0.54761889554039</v>
       </c>
       <c r="AD12" s="7" t="n">
-        <v>0.9869510269761974</v>
+        <v>1.368836070315151</v>
       </c>
       <c r="AE12" s="7" t="n">
-        <v>0.7478408548428984</v>
+        <v>0.7703900054495522</v>
       </c>
       <c r="AF12" s="7" t="n">
-        <v>16.35</v>
+        <v>17.35</v>
       </c>
       <c r="AG12" s="7" t="n">
-        <v>3.45</v>
+        <v>4.45</v>
       </c>
       <c r="AH12" s="7" t="n">
-        <v>0.1028343892545171</v>
+        <v>0.1087001286100384</v>
       </c>
       <c r="AI12" s="7" t="n">
-        <v>0.04005612640255141</v>
+        <v>0.050473616639225</v>
       </c>
       <c r="AJ12" s="7" t="n">
-        <v>0.3773739055211637</v>
+        <v>0.3759082257407668</v>
       </c>
       <c r="AK12" s="7" t="n">
-        <v>0.6966282852617637</v>
+        <v>0.6805431456974156</v>
       </c>
       <c r="AL12" s="7" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AM12" s="7" t="n">
-        <v>10.68333333333333</v>
+        <v>12.01666666666667</v>
       </c>
       <c r="AN12" s="7" t="n">
-        <v>0.2821742444234817</v>
+        <v>0.398684318669226</v>
       </c>
       <c r="AO12" s="7" t="n">
-        <v>0.6170753744976548</v>
+        <v>0.9451362793530877</v>
       </c>
       <c r="AP12" s="7" t="n">
-        <v>5.209370666279662</v>
+        <v>5.036012446348118</v>
       </c>
       <c r="AQ12" s="7" t="n">
-        <v>3.465633928535972</v>
+        <v>4.719127053635388</v>
       </c>
       <c r="AR12" s="7" t="n">
-        <v>40.2</v>
+        <v>75.68333333333334</v>
       </c>
       <c r="AS12" s="7" t="n">
-        <v>26.06666666666667</v>
+        <v>57.41151666666666</v>
       </c>
       <c r="AT12" s="7" t="n">
-        <v>34.54349490383015</v>
+        <v>67.35824904037362</v>
       </c>
       <c r="AU12" s="7" t="n">
-        <v>22.28483087263108</v>
+        <v>50.57101621965544</v>
       </c>
       <c r="AV12" s="7" t="n">
-        <v>51.55745508034351</v>
+        <v>53.4000653039738</v>
       </c>
       <c r="AW12" s="7" t="n">
-        <v>51.29500712370324</v>
+        <v>52.85108545026524</v>
       </c>
       <c r="AX12" s="7" t="n">
-        <v>29.63088333333333</v>
+        <v>57.18333333333333</v>
       </c>
       <c r="AY12" s="7" t="n">
-        <v>22.58333333333333</v>
+        <v>49.6</v>
       </c>
       <c r="AZ12" s="7" t="n">
-        <v>26.48638220201241</v>
+        <v>52.26279143298722</v>
       </c>
       <c r="BA12" s="7" t="n">
-        <v>19.99284056290314</v>
+        <v>45.61259697139702</v>
       </c>
       <c r="BB12" s="7" t="n">
-        <v>53.63265462737621</v>
+        <v>54.83708806725561</v>
       </c>
       <c r="BC12" s="7" t="n">
-        <v>53.1175099826209</v>
+        <v>55.17652859443188</v>
       </c>
       <c r="BD12" s="7" t="n">
-        <v>91.5</v>
+        <v>181.3</v>
       </c>
       <c r="BE12" s="7" t="n">
-        <v>111.62995</v>
+        <v>208.8333333333333</v>
       </c>
       <c r="BF12" s="7" t="n">
-        <v>98.33734745529641</v>
+        <v>205.8931083138968</v>
       </c>
       <c r="BG12" s="7" t="n">
-        <v>116.4659937592599</v>
+        <v>228.2192552116748</v>
       </c>
       <c r="BH12" s="7" t="n">
-        <v>64.48350652806322</v>
+        <v>68.13892167034642</v>
       </c>
       <c r="BI12" s="7" t="n">
-        <v>62.59932594752209</v>
+        <v>65.56977803368153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PAIR_035</t>
+          <t>PAIR_042</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -2621,32 +2621,32 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>04:07:02</t>
+          <t>23:20:57</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>04:20:12</t>
+          <t>06:06:43</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>02:26:26</t>
+          <t>23:13:05</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>02:40:28</t>
+          <t>04:38:29</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -2655,160 +2655,160 @@
         </is>
       </c>
       <c r="M13" s="5" t="n">
-        <v>100.6</v>
+        <v>7.866666666666788</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>17.5104260598227</v>
+        <v>321.8611957625617</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>13.15565</v>
+        <v>405.7706333333333</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>79.86116714790693</v>
+        <v>64.64531488636605</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>17.59592292311513</v>
+        <v>322.4334194047157</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>14.03436666666667</v>
+        <v>325.4048166666667</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>75.22643525442838</v>
+        <v>63.96489623843365</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>0</v>
+        <v>63.2</v>
       </c>
       <c r="U13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>0</v>
+        <v>0.1119717603069536</v>
       </c>
       <c r="W13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="X13" s="5" t="n">
-        <v>0</v>
+        <v>0.10630230408888</v>
       </c>
       <c r="Y13" s="5" t="n">
         <v>0</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>0</v>
+        <v>14.51666666666667</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>0</v>
+        <v>20.58333333333333</v>
       </c>
       <c r="AB13" s="5" t="n">
-        <v>0</v>
+        <v>0.08215844858586425</v>
       </c>
       <c r="AC13" s="5" t="n">
-        <v>0</v>
+        <v>0.4766783541068861</v>
       </c>
       <c r="AD13" s="5" t="n">
-        <v>0</v>
+        <v>0.3395756772779693</v>
       </c>
       <c r="AE13" s="5" t="n">
-        <v>0</v>
+        <v>1.389507752862178</v>
       </c>
       <c r="AF13" s="5" t="n">
-        <v>0</v>
+        <v>29.51666666666667</v>
       </c>
       <c r="AG13" s="5" t="n">
-        <v>0</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="AH13" s="5" t="n">
-        <v>0</v>
+        <v>0.01643615657683831</v>
       </c>
       <c r="AI13" s="5" t="n">
-        <v>0</v>
+        <v>0.0127297174998127</v>
       </c>
       <c r="AJ13" s="5" t="n">
-        <v>0</v>
+        <v>0.03341059496138787</v>
       </c>
       <c r="AK13" s="5" t="n">
-        <v>0</v>
+        <v>0.2695704882313278</v>
       </c>
       <c r="AL13" s="5" t="n">
-        <v>0</v>
+        <v>6.883333333333334</v>
       </c>
       <c r="AM13" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN13" s="5" t="n">
-        <v>0</v>
+        <v>0.5125712172728395</v>
       </c>
       <c r="AO13" s="5" t="n">
-        <v>0</v>
+        <v>0.4202840859765154</v>
       </c>
       <c r="AP13" s="5" t="n">
-        <v>0</v>
+        <v>4.467933128770514</v>
       </c>
       <c r="AQ13" s="5" t="n">
-        <v>0</v>
+        <v>6.304261289647731</v>
       </c>
       <c r="AR13" s="5" t="n">
-        <v>2.366666666666667</v>
+        <v>69.25</v>
       </c>
       <c r="AS13" s="5" t="n">
-        <v>0.5833333333333334</v>
+        <v>45.56666666666667</v>
       </c>
       <c r="AT13" s="5" t="n">
-        <v>3.068290636520454</v>
+        <v>67.11754968426774</v>
       </c>
       <c r="AU13" s="5" t="n">
-        <v>0.6703253541496691</v>
+        <v>40.65136137866402</v>
       </c>
       <c r="AV13" s="5" t="n">
-        <v>77.78764993995516</v>
+        <v>58.15238961813812</v>
       </c>
       <c r="AW13" s="5" t="n">
-        <v>68.9477507125374</v>
+        <v>53.52776187388093</v>
       </c>
       <c r="AX13" s="5" t="n">
-        <v>1.683333333333333</v>
+        <v>57.8873</v>
       </c>
       <c r="AY13" s="5" t="n">
-        <v>0.35</v>
+        <v>33.78333333333333</v>
       </c>
       <c r="AZ13" s="5" t="n">
-        <v>2.206663901320678</v>
+        <v>56.35632166455606</v>
       </c>
       <c r="BA13" s="5" t="n">
-        <v>0.4473149966220811</v>
+        <v>31.65946275202983</v>
       </c>
       <c r="BB13" s="5" t="n">
-        <v>78.65336677974695</v>
+        <v>58.41314588646151</v>
       </c>
       <c r="BC13" s="5" t="n">
-        <v>76.68257084949961</v>
+        <v>56.22795555367903</v>
       </c>
       <c r="BD13" s="5" t="n">
-        <v>9.105650000000001</v>
+        <v>164.5166666666667</v>
       </c>
       <c r="BE13" s="5" t="n">
-        <v>13.10103333333333</v>
+        <v>218.63815</v>
       </c>
       <c r="BF13" s="5" t="n">
-        <v>12.23547152198156</v>
+        <v>197.6641868309954</v>
       </c>
       <c r="BG13" s="5" t="n">
-        <v>16.47828257234338</v>
+        <v>249.2129031164386</v>
       </c>
       <c r="BH13" s="5" t="n">
-        <v>80.62338123240994</v>
+        <v>72.08905608262418</v>
       </c>
       <c r="BI13" s="5" t="n">
-        <v>75.46709707432262</v>
+        <v>68.39050818435079</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>PAIR_038</t>
+          <t>PAIR_048</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>13:53:57</t>
+          <t>11:26:04</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>16:28:14</t>
+          <t>18:16:48</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>14:44:32</t>
+          <t>12:14:31</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>16:14:25</t>
+          <t>18:02:40</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
@@ -2862,25 +2862,25 @@
         </is>
       </c>
       <c r="M14" s="7" t="n">
-        <v>50.58333333333326</v>
+        <v>48.44999999999993</v>
       </c>
       <c r="N14" s="7" t="n">
-        <v>118.6528555237152</v>
+        <v>325.3989070955062</v>
       </c>
       <c r="O14" s="7" t="n">
-        <v>154.2935833333334</v>
+        <v>410.7333333333333</v>
       </c>
       <c r="P14" s="7" t="n">
-        <v>76.62526023529979</v>
+        <v>62.04817090988592</v>
       </c>
       <c r="Q14" s="7" t="n">
-        <v>118.3205529638225</v>
+        <v>324.8843224200924</v>
       </c>
       <c r="R14" s="7" t="n">
-        <v>89.89455</v>
+        <v>348.1472000000001</v>
       </c>
       <c r="S14" s="7" t="n">
-        <v>78.97289855535573</v>
+        <v>63.51275377345894</v>
       </c>
       <c r="T14" s="7" t="n">
         <v>0</v>
@@ -2901,116 +2901,944 @@
         <v>0</v>
       </c>
       <c r="Z14" s="7" t="n">
-        <v>57.05</v>
+        <v>65.98333333333333</v>
       </c>
       <c r="AA14" s="7" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="AB14" s="7" t="n">
-        <v>0.09002709918491375</v>
+        <v>0.2402194601328752</v>
       </c>
       <c r="AC14" s="7" t="n">
-        <v>0</v>
+        <v>0.4503679422720615</v>
       </c>
       <c r="AD14" s="7" t="n">
-        <v>0.0946823129026262</v>
+        <v>0.2184364881228469</v>
       </c>
       <c r="AE14" s="7" t="n">
-        <v>0</v>
+        <v>0.7633354953763755</v>
       </c>
       <c r="AF14" s="7" t="n">
-        <v>4.5</v>
+        <v>30.53333333333333</v>
       </c>
       <c r="AG14" s="7" t="n">
-        <v>0</v>
+        <v>6.316666666666666</v>
       </c>
       <c r="AH14" s="7" t="n">
-        <v>0.1211416233489353</v>
+        <v>0.2158637009068103</v>
       </c>
       <c r="AI14" s="7" t="n">
-        <v>0</v>
+        <v>0.06317093999191636</v>
       </c>
       <c r="AJ14" s="7" t="n">
-        <v>1.615221644652471</v>
+        <v>0.4241863118256098</v>
       </c>
       <c r="AK14" s="7" t="n">
-        <v>0</v>
+        <v>0.6000405909522399</v>
       </c>
       <c r="AL14" s="7" t="n">
-        <v>0.3166666666666667</v>
+        <v>6.383333333333334</v>
       </c>
       <c r="AM14" s="7" t="n">
-        <v>1</v>
+        <v>10.35</v>
       </c>
       <c r="AN14" s="7" t="n">
-        <v>0.01887125568339211</v>
+        <v>0.598015576168782</v>
       </c>
       <c r="AO14" s="7" t="n">
-        <v>0.03644173622497521</v>
+        <v>0.9160590253823516</v>
       </c>
       <c r="AP14" s="7" t="n">
-        <v>3.575606340011136</v>
+        <v>5.621034136312311</v>
       </c>
       <c r="AQ14" s="7" t="n">
-        <v>2.186504173498513</v>
+        <v>5.310487103665807</v>
       </c>
       <c r="AR14" s="7" t="n">
-        <v>19.22816666666667</v>
+        <v>76.56666666666666</v>
       </c>
       <c r="AS14" s="7" t="n">
-        <v>14.0627</v>
+        <v>65.8</v>
       </c>
       <c r="AT14" s="7" t="n">
-        <v>21.56383013715203</v>
+        <v>71.21683905800106</v>
       </c>
       <c r="AU14" s="7" t="n">
-        <v>15.34811928295864</v>
+        <v>59.81880415688165</v>
       </c>
       <c r="AV14" s="7" t="n">
-        <v>67.28825637194332</v>
+        <v>55.80771018911707</v>
       </c>
       <c r="AW14" s="7" t="n">
-        <v>65.48437760725311</v>
+        <v>54.54602202755166</v>
       </c>
       <c r="AX14" s="7" t="n">
-        <v>15.13208333333333</v>
+        <v>59.98333333333333</v>
       </c>
       <c r="AY14" s="7" t="n">
-        <v>10.1</v>
+        <v>46.88053333333333</v>
       </c>
       <c r="AZ14" s="7" t="n">
-        <v>17.72416642729523</v>
+        <v>57.6088865102048</v>
       </c>
       <c r="BA14" s="7" t="n">
-        <v>11.19959394493595</v>
+        <v>44.25115544180538</v>
       </c>
       <c r="BB14" s="7" t="n">
-        <v>70.27783036953805</v>
+        <v>57.62489342504509</v>
       </c>
       <c r="BC14" s="7" t="n">
-        <v>66.53224125704524</v>
+        <v>56.63479354277091</v>
       </c>
       <c r="BD14" s="7" t="n">
-        <v>58.06666666666667</v>
+        <v>171.2833333333333</v>
       </c>
       <c r="BE14" s="7" t="n">
-        <v>64.73184999999999</v>
+        <v>183.4</v>
       </c>
       <c r="BF14" s="7" t="n">
-        <v>79.13481898105066</v>
+        <v>195.5190827900918</v>
       </c>
       <c r="BG14" s="7" t="n">
-        <v>91.736397999703</v>
+        <v>219.3847649137591</v>
       </c>
       <c r="BH14" s="7" t="n">
-        <v>81.76961777605693</v>
+        <v>68.48970497658175</v>
       </c>
       <c r="BI14" s="7" t="n">
-        <v>85.03053566338951</v>
+        <v>71.77255122587539</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Chennai ↔ Pondicherry</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Chennai → Pondicherry</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>13:29:18</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>17:55:07</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>14:27:10</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>19:12:44</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>57.86666666666667</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>153.6764767050815</v>
+      </c>
+      <c r="O15" s="5" t="n">
+        <v>265.8149333333333</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>45.91137366592437</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>153.5307402784298</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>285.5666666666667</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>41.34713516442955</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="5" t="n">
+        <v>35.56666666666667</v>
+      </c>
+      <c r="AA15" s="5" t="n">
+        <v>48.18333333333333</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>0.5933262321891101</v>
+      </c>
+      <c r="AC15" s="5" t="n">
+        <v>0.6526929809004927</v>
+      </c>
+      <c r="AD15" s="5" t="n">
+        <v>1.000925227685471</v>
+      </c>
+      <c r="AE15" s="5" t="n">
+        <v>0.8127619270985035</v>
+      </c>
+      <c r="AF15" s="5" t="n">
+        <v>30.98408333333333</v>
+      </c>
+      <c r="AG15" s="5" t="n">
+        <v>17.66666666666667</v>
+      </c>
+      <c r="AH15" s="5" t="n">
+        <v>0.608277485360332</v>
+      </c>
+      <c r="AI15" s="5" t="n">
+        <v>1.46713538845297</v>
+      </c>
+      <c r="AJ15" s="5" t="n">
+        <v>1.177916052218852</v>
+      </c>
+      <c r="AK15" s="5" t="n">
+        <v>4.982723960783671</v>
+      </c>
+      <c r="AL15" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AM15" s="5" t="n">
+        <v>10.23333333333333</v>
+      </c>
+      <c r="AN15" s="5" t="n">
+        <v>0.3072360563497603</v>
+      </c>
+      <c r="AO15" s="5" t="n">
+        <v>1.325529204266642</v>
+      </c>
+      <c r="AP15" s="5" t="n">
+        <v>5.586110115450188</v>
+      </c>
+      <c r="AQ15" s="5" t="n">
+        <v>7.771832468012887</v>
+      </c>
+      <c r="AR15" s="5" t="n">
+        <v>67.48085</v>
+      </c>
+      <c r="AS15" s="5" t="n">
+        <v>51.03333333333333</v>
+      </c>
+      <c r="AT15" s="5" t="n">
+        <v>47.84822798746782</v>
+      </c>
+      <c r="AU15" s="5" t="n">
+        <v>32.19479692464096</v>
+      </c>
+      <c r="AV15" s="5" t="n">
+        <v>42.54382805267078</v>
+      </c>
+      <c r="AW15" s="5" t="n">
+        <v>37.85149213870263</v>
+      </c>
+      <c r="AX15" s="5" t="n">
+        <v>48.56666666666667</v>
+      </c>
+      <c r="AY15" s="5" t="n">
+        <v>37.13333333333333</v>
+      </c>
+      <c r="AZ15" s="5" t="n">
+        <v>34.79805765976413</v>
+      </c>
+      <c r="BA15" s="5" t="n">
+        <v>24.26414905968165</v>
+      </c>
+      <c r="BB15" s="5" t="n">
+        <v>42.99005064349721</v>
+      </c>
+      <c r="BC15" s="5" t="n">
+        <v>39.20598591330966</v>
+      </c>
+      <c r="BD15" s="5" t="n">
+        <v>79.91666666666667</v>
+      </c>
+      <c r="BE15" s="5" t="n">
+        <v>121.3166666666667</v>
+      </c>
+      <c r="BF15" s="5" t="n">
+        <v>69.52135128395038</v>
+      </c>
+      <c r="BG15" s="5" t="n">
+        <v>93.62643672048709</v>
+      </c>
+      <c r="BH15" s="5" t="n">
+        <v>52.19538365426931</v>
+      </c>
+      <c r="BI15" s="5" t="n">
+        <v>46.30514798650273</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Chennai ↔ Pondicherry</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Pondicherry → Chennai</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>14:31:12</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>18:55:10</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>16:16:08</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>21:02:28</t>
+        </is>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>104.9333333333333</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>151.560156776244</v>
+      </c>
+      <c r="O16" s="7" t="n">
+        <v>263.95295</v>
+      </c>
+      <c r="P16" s="7" t="n">
+        <v>42.41012053032751</v>
+      </c>
+      <c r="Q16" s="7" t="n">
+        <v>152.1093053055016</v>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v>286.3403666666666</v>
+      </c>
+      <c r="S16" s="7" t="n">
+        <v>36.29360732288521</v>
+      </c>
+      <c r="T16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="7" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="AA16" s="7" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AB16" s="7" t="n">
+        <v>0.1862366457606098</v>
+      </c>
+      <c r="AC16" s="7" t="n">
+        <v>0.3661259006707928</v>
+      </c>
+      <c r="AD16" s="7" t="n">
+        <v>0.318353240616427</v>
+      </c>
+      <c r="AE16" s="7" t="n">
+        <v>0.834210912920794</v>
+      </c>
+      <c r="AF16" s="7" t="n">
+        <v>15.11666666666667</v>
+      </c>
+      <c r="AG16" s="7" t="n">
+        <v>10.01666666666667</v>
+      </c>
+      <c r="AH16" s="7" t="n">
+        <v>0.297561165968511</v>
+      </c>
+      <c r="AI16" s="7" t="n">
+        <v>0.5256426997626461</v>
+      </c>
+      <c r="AJ16" s="7" t="n">
+        <v>1.181058652135214</v>
+      </c>
+      <c r="AK16" s="7" t="n">
+        <v>3.148608517713021</v>
+      </c>
+      <c r="AL16" s="7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AM16" s="7" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AN16" s="7" t="n">
+        <v>1.420813179835343</v>
+      </c>
+      <c r="AO16" s="7" t="n">
+        <v>1.205289753214544</v>
+      </c>
+      <c r="AP16" s="7" t="n">
+        <v>12.91648345304857</v>
+      </c>
+      <c r="AQ16" s="7" t="n">
+        <v>5.110769271581105</v>
+      </c>
+      <c r="AR16" s="7" t="n">
+        <v>73.30295</v>
+      </c>
+      <c r="AS16" s="7" t="n">
+        <v>51.26666666666667</v>
+      </c>
+      <c r="AT16" s="7" t="n">
+        <v>52.75602854613859</v>
+      </c>
+      <c r="AU16" s="7" t="n">
+        <v>29.79516392210389</v>
+      </c>
+      <c r="AV16" s="7" t="n">
+        <v>43.18191440819661</v>
+      </c>
+      <c r="AW16" s="7" t="n">
+        <v>34.87080302977048</v>
+      </c>
+      <c r="AX16" s="7" t="n">
+        <v>55.48333333333333</v>
+      </c>
+      <c r="AY16" s="7" t="n">
+        <v>41.04036666666666</v>
+      </c>
+      <c r="AZ16" s="7" t="n">
+        <v>37.95304168068559</v>
+      </c>
+      <c r="BA16" s="7" t="n">
+        <v>24.54736075797758</v>
+      </c>
+      <c r="BB16" s="7" t="n">
+        <v>41.04264044772248</v>
+      </c>
+      <c r="BC16" s="7" t="n">
+        <v>35.88763369102425</v>
+      </c>
+      <c r="BD16" s="7" t="n">
+        <v>78.34999999999999</v>
+      </c>
+      <c r="BE16" s="7" t="n">
+        <v>143.5333333333333</v>
+      </c>
+      <c r="BF16" s="7" t="n">
+        <v>58.94647555785541</v>
+      </c>
+      <c r="BG16" s="7" t="n">
+        <v>95.66972227177216</v>
+      </c>
+      <c r="BH16" s="7" t="n">
+        <v>45.14088747251213</v>
+      </c>
+      <c r="BI16" s="7" t="n">
+        <v>39.99198794454016</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>02-10-2026</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>23:13:07</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>05:06:58</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>23:29:56</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>04:47:52</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="n">
+        <v>16.81666666666683</v>
+      </c>
+      <c r="N17" s="5" t="n">
+        <v>325.4090582064992</v>
+      </c>
+      <c r="O17" s="5" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>67.11318731782285</v>
+      </c>
+      <c r="Q17" s="5" t="n">
+        <v>325.0956316318464</v>
+      </c>
+      <c r="R17" s="5" t="n">
+        <v>317.9467666666667</v>
+      </c>
+      <c r="S17" s="5" t="n">
+        <v>62.7857905819767</v>
+      </c>
+      <c r="T17" s="5" t="n">
+        <v>44.68333333333333</v>
+      </c>
+      <c r="U17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="5" t="n">
+        <v>0.05222273210106956</v>
+      </c>
+      <c r="W17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="5" t="n">
+        <v>0.07012377305626648</v>
+      </c>
+      <c r="Y17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="5" t="n">
+        <v>6.683333333333334</v>
+      </c>
+      <c r="AA17" s="5" t="n">
+        <v>3.016666666666667</v>
+      </c>
+      <c r="AB17" s="5" t="n">
+        <v>0.1270140960027041</v>
+      </c>
+      <c r="AC17" s="5" t="n">
+        <v>0.002166493188354733</v>
+      </c>
+      <c r="AD17" s="5" t="n">
+        <v>1.140276173590361</v>
+      </c>
+      <c r="AE17" s="5" t="n">
+        <v>0.04309047225456927</v>
+      </c>
+      <c r="AF17" s="5" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AG17" s="5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH17" s="5" t="n">
+        <v>0.03154860869050958</v>
+      </c>
+      <c r="AI17" s="5" t="n">
+        <v>0.04085835435001741</v>
+      </c>
+      <c r="AJ17" s="5" t="n">
+        <v>0.1610992784196234</v>
+      </c>
+      <c r="AK17" s="5" t="n">
+        <v>0.5701165723258244</v>
+      </c>
+      <c r="AL17" s="5" t="n">
+        <v>2.016666666666667</v>
+      </c>
+      <c r="AM17" s="5" t="n">
+        <v>1.883333333333333</v>
+      </c>
+      <c r="AN17" s="5" t="n">
+        <v>0.1675031909150123</v>
+      </c>
+      <c r="AO17" s="5" t="n">
+        <v>0.3612962495734293</v>
+      </c>
+      <c r="AP17" s="5" t="n">
+        <v>4.98356601069458</v>
+      </c>
+      <c r="AQ17" s="5" t="n">
+        <v>11.5103229952597</v>
+      </c>
+      <c r="AR17" s="5" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AS17" s="5" t="n">
+        <v>48.91343333333334</v>
+      </c>
+      <c r="AT17" s="5" t="n">
+        <v>59.94209820275543</v>
+      </c>
+      <c r="AU17" s="5" t="n">
+        <v>42.40876109368212</v>
+      </c>
+      <c r="AV17" s="5" t="n">
+        <v>55.93352864953851</v>
+      </c>
+      <c r="AW17" s="5" t="n">
+        <v>52.02099898162115</v>
+      </c>
+      <c r="AX17" s="5" t="n">
+        <v>51.86666666666667</v>
+      </c>
+      <c r="AY17" s="5" t="n">
+        <v>35.33333333333334</v>
+      </c>
+      <c r="AZ17" s="5" t="n">
+        <v>53.82311966809345</v>
+      </c>
+      <c r="BA17" s="5" t="n">
+        <v>30.72869553457691</v>
+      </c>
+      <c r="BB17" s="5" t="n">
+        <v>62.26324897337287</v>
+      </c>
+      <c r="BC17" s="5" t="n">
+        <v>52.18080373796077</v>
+      </c>
+      <c r="BD17" s="5" t="n">
+        <v>172.54785</v>
+      </c>
+      <c r="BE17" s="5" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="BF17" s="5" t="n">
+        <v>211.265551707941</v>
+      </c>
+      <c r="BG17" s="5" t="n">
+        <v>251.5538539064756</v>
+      </c>
+      <c r="BH17" s="5" t="n">
+        <v>73.46329208087182</v>
+      </c>
+      <c r="BI17" s="5" t="n">
+        <v>67.23042866097344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>54</v>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>03-10-2026</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>21:59:13</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>04:56:35</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>22:00:02</t>
+        </is>
+      </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>03:52:46</t>
+        </is>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.816666666666606</v>
+      </c>
+      <c r="N18" s="7" t="n">
+        <v>324.469507401836</v>
+      </c>
+      <c r="O18" s="7" t="n">
+        <v>417.3654666666667</v>
+      </c>
+      <c r="P18" s="7" t="n">
+        <v>64.21541291915878</v>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>325.0334484112802</v>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v>352.7333333333333</v>
+      </c>
+      <c r="S18" s="7" t="n">
+        <v>59.70765591182442</v>
+      </c>
+      <c r="T18" s="7" t="n">
+        <v>34.83333333333334</v>
+      </c>
+      <c r="U18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="7" t="n">
+        <v>0.08893599655368564</v>
+      </c>
+      <c r="W18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="7" t="n">
+        <v>0.1531911902360135</v>
+      </c>
+      <c r="Y18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="7" t="n">
+        <v>58.16666666666666</v>
+      </c>
+      <c r="AA18" s="7" t="n">
+        <v>24.31666666666667</v>
+      </c>
+      <c r="AB18" s="7" t="n">
+        <v>0.3279316256974203</v>
+      </c>
+      <c r="AC18" s="7" t="n">
+        <v>0.4423674542915821</v>
+      </c>
+      <c r="AD18" s="7" t="n">
+        <v>0.3382675795159636</v>
+      </c>
+      <c r="AE18" s="7" t="n">
+        <v>1.091516679540573</v>
+      </c>
+      <c r="AF18" s="7" t="n">
+        <v>21.67998333333333</v>
+      </c>
+      <c r="AG18" s="7" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AH18" s="7" t="n">
+        <v>0.1014181648324159</v>
+      </c>
+      <c r="AI18" s="7" t="n">
+        <v>0.428265735708522</v>
+      </c>
+      <c r="AJ18" s="7" t="n">
+        <v>0.2806777937227022</v>
+      </c>
+      <c r="AK18" s="7" t="n">
+        <v>9.635979053441744</v>
+      </c>
+      <c r="AL18" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM18" s="7" t="n">
+        <v>5.683333333333334</v>
+      </c>
+      <c r="AN18" s="7" t="n">
+        <v>0.5766516264825126</v>
+      </c>
+      <c r="AO18" s="7" t="n">
+        <v>0.5110447249900278</v>
+      </c>
+      <c r="AP18" s="7" t="n">
+        <v>4.324887198618844</v>
+      </c>
+      <c r="AQ18" s="7" t="n">
+        <v>5.395193577607332</v>
+      </c>
+      <c r="AR18" s="7" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="AS18" s="7" t="n">
+        <v>44.46666666666667</v>
+      </c>
+      <c r="AT18" s="7" t="n">
+        <v>63.63085151532849</v>
+      </c>
+      <c r="AU18" s="7" t="n">
+        <v>36.40661394018598</v>
+      </c>
+      <c r="AV18" s="7" t="n">
+        <v>59.19148978170092</v>
+      </c>
+      <c r="AW18" s="7" t="n">
+        <v>49.1243666359331</v>
+      </c>
+      <c r="AX18" s="7" t="n">
+        <v>53.65215</v>
+      </c>
+      <c r="AY18" s="7" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="AZ18" s="7" t="n">
+        <v>53.72863846122127</v>
+      </c>
+      <c r="BA18" s="7" t="n">
+        <v>29.04782298717766</v>
+      </c>
+      <c r="BB18" s="7" t="n">
+        <v>60.08553818762672</v>
+      </c>
+      <c r="BC18" s="7" t="n">
+        <v>53.70937994547487</v>
+      </c>
+      <c r="BD18" s="7" t="n">
+        <v>176.5333333333333</v>
+      </c>
+      <c r="BE18" s="7" t="n">
+        <v>243.15</v>
+      </c>
+      <c r="BF18" s="7" t="n">
+        <v>206.0150800117203</v>
+      </c>
+      <c r="BG18" s="7" t="n">
+        <v>258.1973335689265</v>
+      </c>
+      <c r="BH18" s="7" t="n">
+        <v>70.02023112180827</v>
+      </c>
+      <c r="BI18" s="7" t="n">
+        <v>63.71309896827304</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:BI14"/>
+  <autoFilter ref="A4:BI18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:BI1"/>
   </mergeCells>
@@ -3216,7 +4044,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
